--- a/RAMEN_FINMODEL_Final_NEW_STRUCTURE.xlsx
+++ b/RAMEN_FINMODEL_Final_NEW_STRUCTURE.xlsx
@@ -39,7 +39,7 @@
     <numFmt numFmtId="180" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
     <numFmt numFmtId="181" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
     <numFmt numFmtId="182" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* \-_);_(@_)"/>
-    <numFmt numFmtId="183" formatCode="+0%;−0%;0%"/>
+    <numFmt numFmtId="183" formatCode="+0%;-0%;0%"/>
   </numFmts>
   <fonts count="40">
     <font>
